--- a/data/trans_orig/P15E_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P15E_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años según si ha sufrido alguna caída que precise atención sanitaria en el último año en 2023</t>
+          <t>Población mayor de 65 años según si ha sufrido alguna caída que precise atención sanitaria en el último año en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>937</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11844</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14694</t>
+          <t>14443</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>76,19%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>563</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>492</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>32,87%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>877</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10828</t>
+          <t>11069</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14563</t>
+          <t>14190</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>77,03%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12018</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,92%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12185</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>62,52%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>376</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -2211,97 +2211,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>17,24%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>44,28%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>798</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2054</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>17,24%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>2196</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>11,9%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>44,38%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>2609</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -2554,97 +2554,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>738</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2667,97 +2667,97 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>738</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>326</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,31%</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>875</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11599</t>
+          <t>11373</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>11306</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>16854</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>75,77%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13824</t>
+          <t>14092</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16703</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>73,47%</t>
         </is>
       </c>
     </row>
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>558</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -4035,97 +4035,97 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="R33" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>17857</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>30073</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>28089</t>
+          <t>28475</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>42797</t>
+          <t>42753</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>456</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13729</t>
+          <t>14225</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>16327</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>15102</t>
+          <t>15134</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>24402</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>43189</t>
+          <t>44458</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>56048</t>
+          <t>56894</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>62366</t>
+          <t>62743</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>78462</t>
+          <t>78283</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15E_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P15E_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>688</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>504</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>4337</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>12147</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>9155</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14443</t>
+          <t>15083</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,85%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>13889</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>13889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>13889</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>19627</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>19627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>19627</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>534</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11069</t>
+          <t>11631</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14190</t>
+          <t>15124</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>19573</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>19573</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>19573</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9045</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12090</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>65,56%</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>650</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>398</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>63,45%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7953</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7953</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7953</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>11087</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>11087</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>11087</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>410</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>368</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>822</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>822</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>345</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>36,73%</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>772</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11373</t>
+          <t>11925</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11306</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16935</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>22581</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>22581</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>22581</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>791</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>12354</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>44,91%</t>
         </is>
       </c>
     </row>
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>847</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14092</t>
+          <t>16767</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>13188</t>
+          <t>16743</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>20991</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>76,3%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>17436</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17436</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17436</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>22025</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>22025</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>22025</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>659</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2443</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,07%</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>667</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>87,06%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4373,32 +4373,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,32 +4408,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>24102</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>17857</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>35127</t>
+          <t>37813</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>28475</t>
+          <t>30407</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>42753</t>
+          <t>45323</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -4486,32 +4486,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>14225</t>
+          <t>14329</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>11740</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>16401</t>
+          <t>17433</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -4599,32 +4599,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>22283</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>17206</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>24402</t>
+          <t>27180</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,32 +4634,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>50613</t>
+          <t>55272</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>44458</t>
+          <t>48615</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>56894</t>
+          <t>61589</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>70474</t>
+          <t>77555</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>62743</t>
+          <t>69640</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>78283</t>
+          <t>85882</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,57%</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4712,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
